--- a/Lineup 2026.xlsx
+++ b/Lineup 2026.xlsx
@@ -166,16 +166,46 @@
     <t xml:space="preserve">BREAK (Water/Tea) </t>
   </si>
   <si>
+    <t>ডনা, ৰায়ান আৰু আশিৰ নৃত্য</t>
+  </si>
+  <si>
+    <t>Dona, Ryan and Aashi dance</t>
+  </si>
+  <si>
+    <t>একক গীত – আনিশা</t>
+  </si>
+  <si>
+    <t>Solo song Anisha</t>
+  </si>
+  <si>
+    <t>কথক নৃত্য</t>
+  </si>
+  <si>
+    <t>kathak dance by Aarna</t>
+  </si>
+  <si>
     <t>অসমীয়া আধুনিক নৃত্য</t>
   </si>
   <si>
     <t>Assamese Modern dance (Anita's group)</t>
   </si>
   <si>
-    <t>ভাষণ</t>
+    <t>Nitu</t>
   </si>
   <si>
-    <t xml:space="preserve">Speech </t>
+    <t>Mausumi</t>
+  </si>
+  <si>
+    <t>একক গীত – অগস্ত্য</t>
+  </si>
+  <si>
+    <t>Solo song Agastya</t>
+  </si>
+  <si>
+    <t>কলিজা ঢিপিশ ঢিপিশ</t>
+  </si>
+  <si>
+    <t>Kalija dhipish dhipish</t>
   </si>
   <si>
     <t xml:space="preserve">একক গীত </t>
@@ -184,40 +214,10 @@
     <t>Pankaj song</t>
   </si>
   <si>
-    <t>কলিজা ঢিপিশ ঢিপিশ</t>
+    <t>ভাষণ</t>
   </si>
   <si>
-    <t>Kalija dhipish dhipish</t>
-  </si>
-  <si>
-    <t>Nitu</t>
-  </si>
-  <si>
-    <t>Mausumi</t>
-  </si>
-  <si>
-    <t>একক গীত – আনিশা</t>
-  </si>
-  <si>
-    <t>Solo song Anisha</t>
-  </si>
-  <si>
-    <t>ডনা আৰু আশিৰ নৃত্য</t>
-  </si>
-  <si>
-    <t>Dona and Aashi dance</t>
-  </si>
-  <si>
-    <t>একক গীত – অগস্ত্য</t>
-  </si>
-  <si>
-    <t>Solo song Agastya</t>
-  </si>
-  <si>
-    <t>কথক নৃত্য</t>
-  </si>
-  <si>
-    <t>kathak dance by Aarna</t>
+    <t xml:space="preserve">Speech </t>
   </si>
   <si>
     <t>সংগীতানুষ্ঠান</t>
@@ -421,7 +421,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -498,7 +498,13 @@
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
@@ -1587,10 +1593,10 @@
       <c r="A20" s="24">
         <v>18.0</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D20" s="16">
@@ -1629,7 +1635,7 @@
       <c r="A21" s="24">
         <v>19.0</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="12" t="s">
@@ -1673,7 +1679,7 @@
       <c r="A22" s="18">
         <v>20.0</v>
       </c>
-      <c r="B22" s="25" t="s">
+      <c r="B22" s="5" t="s">
         <v>55</v>
       </c>
       <c r="C22" s="12" t="s">
@@ -1684,10 +1690,10 @@
       </c>
       <c r="E22" s="17">
         <f t="shared" si="1"/>
-        <v>0.7961805556</v>
+        <v>0.7954861111</v>
       </c>
-      <c r="F22" s="15">
-        <v>3.0</v>
+      <c r="F22" s="27">
+        <v>2.0</v>
       </c>
       <c r="G22" s="4"/>
       <c r="H22" s="4"/>
@@ -1730,8 +1736,8 @@
         <f t="shared" si="1"/>
         <v>0.8010416667</v>
       </c>
-      <c r="F23" s="15">
-        <v>2.0</v>
+      <c r="F23" s="27">
+        <v>3.0</v>
       </c>
       <c r="G23" s="4"/>
       <c r="H23" s="4" t="s">
@@ -1765,7 +1771,7 @@
       <c r="A24" s="24">
         <v>22.0</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="12" t="s">
@@ -1809,7 +1815,7 @@
       <c r="A25" s="18">
         <v>23.0</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -1853,7 +1859,7 @@
       <c r="A26" s="24">
         <v>24.0</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="26" t="s">
         <v>65</v>
       </c>
       <c r="C26" s="12" t="s">
@@ -1941,7 +1947,7 @@
       <c r="A28" s="18">
         <v>26.0</v>
       </c>
-      <c r="B28" s="25" t="s">
+      <c r="B28" s="26" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="12" t="s">
@@ -2029,7 +2035,7 @@
       <c r="A30" s="24">
         <v>28.0</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="26" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="12" t="s">
@@ -2073,7 +2079,7 @@
       <c r="A31" s="18">
         <v>29.0</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="26" t="s">
         <v>75</v>
       </c>
       <c r="C31" s="12" t="s">
@@ -2117,7 +2123,7 @@
       <c r="A32" s="24">
         <v>30.0</v>
       </c>
-      <c r="B32" s="25" t="s">
+      <c r="B32" s="26" t="s">
         <v>77</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -2207,7 +2213,7 @@
       <c r="A34" s="18">
         <v>32.0</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="26" t="s">
         <v>81</v>
       </c>
       <c r="C34" s="12" t="s">
@@ -2251,7 +2257,7 @@
       <c r="A35" s="24">
         <v>33.0</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="26" t="s">
         <v>69</v>
       </c>
       <c r="C35" s="12" t="s">
@@ -2295,7 +2301,7 @@
       <c r="A36" s="24">
         <v>34.0</v>
       </c>
-      <c r="B36" s="25" t="s">
+      <c r="B36" s="26" t="s">
         <v>84</v>
       </c>
       <c r="C36" s="12" t="s">
@@ -2383,7 +2389,7 @@
       <c r="A38" s="18">
         <v>36.0</v>
       </c>
-      <c r="B38" s="25" t="s">
+      <c r="B38" s="26" t="s">
         <v>88</v>
       </c>
       <c r="C38" s="12" t="s">
@@ -2427,7 +2433,7 @@
       <c r="A39" s="24">
         <v>37.0</v>
       </c>
-      <c r="B39" s="25" t="s">
+      <c r="B39" s="26" t="s">
         <v>90</v>
       </c>
       <c r="C39" s="12" t="s">
@@ -2527,11 +2533,11 @@
       <c r="C41" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D41" s="26">
+      <c r="D41" s="28">
         <v>60.0</v>
       </c>
-      <c r="E41" s="27"/>
-      <c r="F41" s="28"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="30"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2599,7 +2605,7 @@
       <c r="A43" s="24">
         <v>41.0</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B43" s="26" t="s">
         <v>99</v>
       </c>
       <c r="C43" s="12" t="s">

--- a/Lineup 2026.xlsx
+++ b/Lineup 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="142">
   <si>
     <t>sequenceId</t>
   </si>
@@ -31,16 +31,16 @@
     <t>prepTime</t>
   </si>
   <si>
-    <t>artist(s)</t>
+    <t>perfomers/speakers</t>
   </si>
   <si>
-    <t>Overlaps</t>
+    <t>Coordinator</t>
   </si>
   <si>
     <t xml:space="preserve">জলপান , আলোকচিত্ৰ </t>
   </si>
   <si>
-    <t xml:space="preserve">Snacks + Photo </t>
+    <t xml:space="preserve">Snacks, Photo </t>
   </si>
   <si>
     <t>উদ্বোধনী ভাষণ</t>
@@ -55,7 +55,7 @@
     <t>Adult Chorus</t>
   </si>
   <si>
-    <t>Abhijit, Manoj</t>
+    <t>Anita,Tisha,Papari, Jyotishman, Diya, Pallavi K., Karabi(Amar),rajeev, Abhijit, Manoj</t>
   </si>
   <si>
     <t>শিশুসকলৰ সমবেত সংগীত</t>
@@ -64,7 +64,43 @@
     <t>Kids Chorus</t>
   </si>
   <si>
-    <t xml:space="preserve">Agastya, </t>
+    <t>Nirvan,Navya,Abishta,Aadvik,Anisha,Sayesha, Aarna, Bishakha, Aashi, Jinisha, Ziyan, Alaina,Drishana,Gionna,Ishika</t>
+  </si>
+  <si>
+    <t>Manoj, Tuki</t>
+  </si>
+  <si>
+    <t>লিটল গ্ৰুভাৰছ</t>
+  </si>
+  <si>
+    <t>Little Groovers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anaisha &amp; Drivika </t>
+  </si>
+  <si>
+    <t>Sue, Soma</t>
+  </si>
+  <si>
+    <t>সৰু ছোৱালীৰ নৃত্য</t>
+  </si>
+  <si>
+    <t>Little girl's dance (8-10 yrs)</t>
+  </si>
+  <si>
+    <t>Aarna, Anisha, Jinisha , Aashi</t>
+  </si>
+  <si>
+    <t>Pranami, Ritu</t>
+  </si>
+  <si>
+    <t>শিশু নৃত্য</t>
+  </si>
+  <si>
+    <t>Kids dance (6-9 age group)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nirvan, Aadvik, Rishik, Ishika, Myra, Sayesha, Evaan, Sanya </t>
   </si>
   <si>
     <t>সত্ৰীয়া নৃত্য</t>
@@ -73,19 +109,22 @@
     <t>Xatriya</t>
   </si>
   <si>
-    <t>Nerina &amp; team</t>
+    <t>Dashavatar Group</t>
   </si>
   <si>
-    <t>লিটল গ্ৰুভাৰছ</t>
+    <t>Nerina</t>
   </si>
   <si>
-    <t>Little Groovers</t>
+    <t>জীয়ৰীসকলৰ বিহু</t>
   </si>
   <si>
-    <t>সৰু ছোৱালীৰ নৃত্য</t>
+    <t>Daughters Bihu</t>
   </si>
   <si>
-    <t>Little girl's dance (8-10 yrs)</t>
+    <t>Tuhina, Tulika</t>
+  </si>
+  <si>
+    <t>Kalpita</t>
   </si>
   <si>
     <t>পোছাক প্ৰদৰ্শনী</t>
@@ -94,37 +133,7 @@
     <t>Fashion Show</t>
   </si>
   <si>
-    <t>Soma, Patinita</t>
-  </si>
-  <si>
-    <t>Jonali</t>
-  </si>
-  <si>
-    <t>Donna</t>
-  </si>
-  <si>
-    <t>জীয়ৰীসকলৰ বিহু</t>
-  </si>
-  <si>
-    <t>Kalpita daughter Bihu</t>
-  </si>
-  <si>
-    <t>শিশু নৃত্য</t>
-  </si>
-  <si>
-    <t>Kids dance (6-9 age group)</t>
-  </si>
-  <si>
-    <t>মিছি গীত</t>
-  </si>
-  <si>
-    <t>Mishi (Ishita) Song</t>
-  </si>
-  <si>
-    <t>কে-পপ গোল্ডেন</t>
-  </si>
-  <si>
-    <t>Kay pop golden (Pahi/Navin)</t>
+    <t>Karabi Sharma</t>
   </si>
   <si>
     <t>সাত ভগিনীৰ নৃত্য</t>
@@ -133,10 +142,52 @@
     <t>Seven sisters dance</t>
   </si>
   <si>
+    <t xml:space="preserve">Seven Sisters </t>
+  </si>
+  <si>
+    <t>Kalpita, Sanjukta</t>
+  </si>
+  <si>
+    <t>মিছিৰ গীত</t>
+  </si>
+  <si>
+    <t>Solo Song</t>
+  </si>
+  <si>
+    <t>Mishi</t>
+  </si>
+  <si>
+    <t>কে-পপ গোল্ডেন</t>
+  </si>
+  <si>
+    <t>Kay pop golden</t>
+  </si>
+  <si>
+    <t>Sayesha,Ishika, Sanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pahi, Navin</t>
+  </si>
+  <si>
     <t>একক গীত –</t>
   </si>
   <si>
     <t>Solo song Jinisha</t>
+  </si>
+  <si>
+    <t>Jinisha</t>
+  </si>
+  <si>
+    <t>পিয়ানো</t>
+  </si>
+  <si>
+    <t>Piano</t>
+  </si>
+  <si>
+    <t>Arohi</t>
+  </si>
+  <si>
+    <t>Barnali</t>
   </si>
   <si>
     <t>লুইতৰ লুইটী</t>
@@ -145,19 +196,19 @@
     <t>Luitor Luiti (Mother Daughter Dance)</t>
   </si>
   <si>
-    <t>Soma Parinita</t>
+    <t>Drishana, Kashvi, Parinita, Soma</t>
   </si>
   <si>
-    <t>মহিলাৰ বিহু</t>
+    <t>Parinita, Soma</t>
   </si>
   <si>
-    <t>Ladies Bihu</t>
+    <t>বিহুৱতীৰ বিহু</t>
   </si>
   <si>
-    <t>পিয়ানো</t>
+    <t>Bihuwotir Bihu</t>
   </si>
   <si>
-    <t>Piano</t>
+    <t>Jonali, Ruby, Priyanka, Sue, Ritu, Dona, Kalpita, Karabi(s), Janu</t>
   </si>
   <si>
     <t>চাহ-পানীৰ অৱকাশ</t>
@@ -166,16 +217,25 @@
     <t xml:space="preserve">BREAK (Water/Tea) </t>
   </si>
   <si>
+    <t>একক গীত – আনিশা</t>
+  </si>
+  <si>
+    <t>Solo song Anisha</t>
+  </si>
+  <si>
+    <t>Anisha</t>
+  </si>
+  <si>
     <t>ডনা, ৰায়ান আৰু আশিৰ নৃত্য</t>
   </si>
   <si>
     <t>Dona, Ryan and Aashi dance</t>
   </si>
   <si>
-    <t>একক গীত – আনিশা</t>
+    <t>Dona, Ryan, Ashi</t>
   </si>
   <si>
-    <t>Solo song Anisha</t>
+    <t>Dona</t>
   </si>
   <si>
     <t>কথক নৃত্য</t>
@@ -184,22 +244,104 @@
     <t>kathak dance by Aarna</t>
   </si>
   <si>
+    <t>Aarna</t>
+  </si>
+  <si>
     <t>অসমীয়া আধুনিক নৃত্য</t>
   </si>
   <si>
-    <t>Assamese Modern dance (Anita's group)</t>
+    <t xml:space="preserve">Assamese Modern dance </t>
   </si>
   <si>
-    <t>Nitu</t>
+    <t xml:space="preserve">Navya, Lisa, Bishakha, Alaina ,Gionna, Mishi
+</t>
   </si>
   <si>
-    <t>Mausumi</t>
+    <t>Mausumi, Anita and Tisha</t>
   </si>
   <si>
     <t>একক গীত – অগস্ত্য</t>
   </si>
   <si>
-    <t>Solo song Agastya</t>
+    <t xml:space="preserve">Solo song </t>
+  </si>
+  <si>
+    <t>Agastya</t>
+  </si>
+  <si>
+    <t>নাচলে স্কোৱাড</t>
+  </si>
+  <si>
+    <t>Nachley squad</t>
+  </si>
+  <si>
+    <t>Pranami, Jyotishikha, Nitu K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">একক গীত </t>
+  </si>
+  <si>
+    <t>Pankaj</t>
+  </si>
+  <si>
+    <t>ভাষণ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speech </t>
+  </si>
+  <si>
+    <t>Saibal&amp; Tuki</t>
+  </si>
+  <si>
+    <t>সংগীতানুষ্ঠান</t>
+  </si>
+  <si>
+    <t>XYZ musical</t>
+  </si>
+  <si>
+    <t>Loy, Mrinmoy, Paahi, Rishab</t>
+  </si>
+  <si>
+    <t>Mrinmoy</t>
+  </si>
+  <si>
+    <t>লোক নৃত্য</t>
+  </si>
+  <si>
+    <t>Folk dance</t>
+  </si>
+  <si>
+    <t>Pallavi K., Anita, Erica, Papari,  Jonali, Loona, Nita</t>
+  </si>
+  <si>
+    <t>Jonali</t>
+  </si>
+  <si>
+    <t>একক গীত – কৰবী শৰ্মা</t>
+  </si>
+  <si>
+    <t>Solo song Karabi Sarma</t>
+  </si>
+  <si>
+    <t>Karabi Sarmah</t>
+  </si>
+  <si>
+    <t>ৰাহুল আৰু অঞ্চিতা</t>
+  </si>
+  <si>
+    <t>Rahul and Anchita</t>
+  </si>
+  <si>
+    <t>Rahul, Anchita</t>
+  </si>
+  <si>
+    <t>ৰিশিতাৰ নৃত্য</t>
+  </si>
+  <si>
+    <t>Rishita dance</t>
+  </si>
+  <si>
+    <t>Rishita</t>
   </si>
   <si>
     <t>কলিজা ঢিপিশ ঢিপিশ</t>
@@ -208,52 +350,10 @@
     <t>Kalija dhipish dhipish</t>
   </si>
   <si>
-    <t xml:space="preserve">একক গীত </t>
+    <t>Mousumi, Nitu K., Arohi, Simanta P.</t>
   </si>
   <si>
-    <t>Pankaj song</t>
-  </si>
-  <si>
-    <t>ভাষণ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speech </t>
-  </si>
-  <si>
-    <t>সংগীতানুষ্ঠান</t>
-  </si>
-  <si>
-    <t>XYZ musical</t>
-  </si>
-  <si>
-    <t>লোক নৃত্য</t>
-  </si>
-  <si>
-    <t>Folk dance</t>
-  </si>
-  <si>
-    <t>একক গীত – কৰবী শৰ্মা</t>
-  </si>
-  <si>
-    <t>Solo song Karabi Sarma</t>
-  </si>
-  <si>
-    <t>ৰাহুল আৰু অঞ্চিতা</t>
-  </si>
-  <si>
-    <t>Rahul and Anchita</t>
-  </si>
-  <si>
-    <t>ৰিশিতাৰ নৃত্য</t>
-  </si>
-  <si>
-    <t>Rishita dance</t>
-  </si>
-  <si>
-    <t>নাচলে স্কোৱাড</t>
-  </si>
-  <si>
-    <t>Nachley squad</t>
+    <t>Simanta P.</t>
   </si>
   <si>
     <t>একক গীত – দীয়া</t>
@@ -262,19 +362,34 @@
     <t>Solo song Diya</t>
   </si>
   <si>
+    <t>Diya</t>
+  </si>
+  <si>
     <t>ABC musical</t>
+  </si>
+  <si>
+    <t>Rajeev</t>
   </si>
   <si>
     <t>একক গীত – নিতু প্ৰধানী</t>
   </si>
   <si>
-    <t>solo song Nitu Pradhani</t>
+    <t xml:space="preserve">solo song </t>
   </si>
   <si>
-    <t>গোট অৰ্কেষ্ট্ৰা – মৃন্ময়</t>
+    <t>Nitu Pradhani</t>
   </si>
   <si>
-    <t>group orchestra Mrinmoy</t>
+    <t>জুবিন গাৰ্গ স্পেচিয়েল</t>
+  </si>
+  <si>
+    <t>Zubeen Garg Special</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anita, Jyotishman, Mausumi, Tisha, Mrinmoy, Pallavi K. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jyotishman </t>
   </si>
   <si>
     <t>কবিতা – অঞ্জনা বৰা</t>
@@ -283,19 +398,25 @@
     <t>Poem anjana bora</t>
   </si>
   <si>
-    <t>জুবিন গাৰ্গ স্পেচিয়েল</t>
-  </si>
-  <si>
-    <t>Zubeen Garg Special</t>
-  </si>
-  <si>
-    <t>Anita, Pallavi</t>
+    <t>Anjana Bora</t>
   </si>
   <si>
     <t>ঢিনিকি ঢিন দাও</t>
   </si>
   <si>
     <t>Dhiniki Dhin dau</t>
+  </si>
+  <si>
+    <t>Rongali Rockers</t>
+  </si>
+  <si>
+    <t>Dhurandhar</t>
+  </si>
+  <si>
+    <t>গোট অৰ্কেষ্ট্ৰা – মৃন্ময়</t>
+  </si>
+  <si>
+    <t>Orchestra Mrinmoy</t>
   </si>
   <si>
     <t>নিশাৰ আহাৰ</t>
@@ -323,7 +444,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -344,6 +465,22 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="16.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -421,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -453,7 +590,7 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
@@ -465,7 +602,7 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -476,10 +613,31 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -494,26 +652,23 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="1" numFmtId="20" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -733,7 +888,11 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="2" max="2" width="28.38"/>
-    <col customWidth="1" min="3" max="3" width="54.88"/>
+    <col customWidth="1" min="3" max="3" width="38.0"/>
+    <col customWidth="1" min="4" max="4" width="5.63"/>
+    <col customWidth="1" min="5" max="5" width="12.88"/>
+    <col customWidth="1" min="6" max="6" width="8.13"/>
+    <col customWidth="1" min="7" max="7" width="51.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -755,15 +914,13 @@
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="I1" s="4"/>
       <c r="J1" s="4"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
@@ -799,7 +956,7 @@
         <v>60.0</v>
       </c>
       <c r="E2" s="10">
-        <v>0.6458333333333334</v>
+        <v>0.625</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -840,7 +997,7 @@
         <v>3.0</v>
       </c>
       <c r="E3" s="14">
-        <v>0.6875</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F3" s="15">
         <v>0.0</v>
@@ -884,12 +1041,12 @@
       </c>
       <c r="E4" s="17">
         <f t="shared" ref="E4:E40" si="1">E3+(D3+ F4)/1440</f>
-        <v>0.6909722222</v>
+        <v>0.6701388889</v>
       </c>
       <c r="F4" s="15">
         <v>2.0</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="18" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="4"/>
@@ -930,15 +1087,17 @@
       </c>
       <c r="E5" s="17">
         <f t="shared" si="1"/>
-        <v>0.6958333333</v>
+        <v>0.675</v>
       </c>
       <c r="F5" s="15">
         <v>2.0</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H5" s="19" t="s">
+        <v>18</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
@@ -962,29 +1121,31 @@
       <c r="AC5" s="5"/>
     </row>
     <row r="6">
-      <c r="A6" s="6">
+      <c r="A6" s="20">
         <v>4.0</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="16">
-        <v>5.5</v>
+        <v>5.0</v>
       </c>
       <c r="E6" s="17">
         <f t="shared" si="1"/>
-        <v>0.7006944444</v>
+        <v>0.6798611111</v>
       </c>
       <c r="F6" s="15">
         <v>2.0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>20</v>
+      <c r="G6" s="18" t="s">
+        <v>21</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5"/>
@@ -1008,27 +1169,31 @@
       <c r="AC6" s="5"/>
     </row>
     <row r="7">
-      <c r="A7" s="6">
+      <c r="A7" s="20">
         <v>5.0</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D7" s="16">
         <v>5.0</v>
       </c>
       <c r="E7" s="17">
         <f t="shared" si="1"/>
-        <v>0.7059027778</v>
+        <v>0.6847222222</v>
       </c>
       <c r="F7" s="15">
         <v>2.0</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="G7" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="5"/>
@@ -1052,26 +1217,28 @@
       <c r="AC7" s="5"/>
     </row>
     <row r="8">
-      <c r="A8" s="6">
+      <c r="A8" s="20">
         <v>6.0</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D8" s="16">
         <v>5.0</v>
       </c>
       <c r="E8" s="17">
         <f t="shared" si="1"/>
-        <v>0.7107638889</v>
+        <v>0.6895833333</v>
       </c>
       <c r="F8" s="15">
         <v>2.0</v>
       </c>
-      <c r="G8" s="4"/>
+      <c r="G8" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1096,35 +1263,33 @@
       <c r="AC8" s="5"/>
     </row>
     <row r="9">
-      <c r="A9" s="6">
+      <c r="A9" s="20">
         <v>7.0</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D9" s="16">
-        <v>10.0</v>
+        <v>5.5</v>
       </c>
       <c r="E9" s="17">
         <f t="shared" si="1"/>
-        <v>0.7170138889</v>
+        <v>0.6944444444</v>
       </c>
       <c r="F9" s="15">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4" t="s">
-        <v>27</v>
+      <c r="G9" s="18" t="s">
+        <v>32</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>28</v>
+      <c r="H9" s="2" t="s">
+        <v>33</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>29</v>
-      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5"/>
@@ -1150,23 +1315,27 @@
         <v>8.0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>31</v>
+      <c r="C10" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D10" s="16">
         <v>5.0</v>
       </c>
       <c r="E10" s="17">
         <f t="shared" si="1"/>
-        <v>0.7253472222</v>
+        <v>0.6996527778</v>
       </c>
       <c r="F10" s="15">
         <v>2.0</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="G10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="5"/>
@@ -1190,27 +1359,29 @@
       <c r="AC10" s="5"/>
     </row>
     <row r="11">
-      <c r="A11" s="6">
+      <c r="A11" s="20">
         <v>9.0</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D11" s="16">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="E11" s="17">
         <f t="shared" si="1"/>
-        <v>0.7302083333</v>
+        <v>0.7059027778</v>
       </c>
       <c r="F11" s="15">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="H11" s="19" t="s">
+        <v>40</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="5"/>
@@ -1234,27 +1405,31 @@
       <c r="AC11" s="5"/>
     </row>
     <row r="12">
-      <c r="A12" s="6">
+      <c r="A12" s="20">
         <v>10.0</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>34</v>
+      <c r="B12" s="21" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D12" s="16">
         <v>5.0</v>
       </c>
       <c r="E12" s="17">
         <f t="shared" si="1"/>
-        <v>0.734375</v>
+        <v>0.7142361111</v>
       </c>
       <c r="F12" s="15">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="G12" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="5"/>
@@ -1278,26 +1453,28 @@
       <c r="AC12" s="5"/>
     </row>
     <row r="13">
-      <c r="A13" s="6">
+      <c r="A13" s="20">
         <v>11.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>36</v>
+      <c r="B13" s="21" t="s">
+        <v>45</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>37</v>
+      <c r="C13" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="D13" s="16">
         <v>5.0</v>
       </c>
       <c r="E13" s="17">
         <f t="shared" si="1"/>
-        <v>0.7385416667</v>
+        <v>0.7184027778</v>
       </c>
       <c r="F13" s="15">
         <v>1.0</v>
       </c>
-      <c r="G13" s="4"/>
+      <c r="G13" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1322,27 +1499,31 @@
       <c r="AC13" s="5"/>
     </row>
     <row r="14">
-      <c r="A14" s="6">
+      <c r="A14" s="20">
         <v>12.0</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
-      <c r="C14" s="12" t="s">
-        <v>39</v>
+      <c r="C14" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D14" s="16">
         <v>5.0</v>
       </c>
       <c r="E14" s="17">
         <f t="shared" si="1"/>
-        <v>0.7434027778</v>
+        <v>0.7225694444</v>
       </c>
       <c r="F14" s="15">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="G14" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>51</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="5"/>
@@ -1370,22 +1551,24 @@
         <v>13.0</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="D15" s="16">
         <v>5.0</v>
       </c>
       <c r="E15" s="17">
         <f t="shared" si="1"/>
-        <v>0.7475694444</v>
+        <v>0.7267361111</v>
       </c>
       <c r="F15" s="15">
         <v>1.0</v>
       </c>
-      <c r="G15" s="4"/>
+      <c r="G15" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1410,28 +1593,30 @@
       <c r="AC15" s="5"/>
     </row>
     <row r="16">
-      <c r="A16" s="6">
+      <c r="A16" s="20">
         <v>14.0</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="D16" s="16">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="E16" s="17">
         <f t="shared" si="1"/>
-        <v>0.7524305556</v>
+        <v>0.7315972222</v>
       </c>
       <c r="F16" s="15">
         <v>2.0</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4" t="s">
-        <v>44</v>
+      <c r="G16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -1456,33 +1641,33 @@
       <c r="AC16" s="5"/>
     </row>
     <row r="17">
-      <c r="A17" s="6">
+      <c r="A17" s="20">
         <v>15.0</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="D17" s="16">
         <v>5.0</v>
       </c>
       <c r="E17" s="17">
         <f t="shared" si="1"/>
-        <v>0.7579861111</v>
+        <v>0.7350694444</v>
       </c>
       <c r="F17" s="15">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4" t="s">
-        <v>28</v>
+      <c r="G17" s="18" t="s">
+        <v>61</v>
       </c>
-      <c r="J17" s="4" t="s">
-        <v>29</v>
+      <c r="H17" s="19" t="s">
+        <v>62</v>
       </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5"/>
@@ -1504,26 +1689,28 @@
       <c r="AC17" s="5"/>
     </row>
     <row r="18">
-      <c r="A18" s="6">
+      <c r="A18" s="20">
         <v>16.0</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>47</v>
+      <c r="B18" s="21" t="s">
+        <v>63</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>48</v>
+      <c r="C18" s="8" t="s">
+        <v>64</v>
       </c>
-      <c r="D18" s="16">
-        <v>3.0</v>
+      <c r="D18" s="24">
+        <v>7.0</v>
       </c>
       <c r="E18" s="17">
         <f t="shared" si="1"/>
-        <v>0.7628472222</v>
+        <v>0.740625</v>
       </c>
       <c r="F18" s="15">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
-      <c r="G18" s="4"/>
+      <c r="G18" s="18" t="s">
+        <v>65</v>
+      </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -1548,23 +1735,23 @@
       <c r="AC18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="18">
+      <c r="A19" s="25">
         <v>17.0</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>49</v>
+      <c r="B19" s="26" t="s">
+        <v>66</v>
       </c>
-      <c r="C19" s="20" t="s">
-        <v>50</v>
+      <c r="C19" s="27" t="s">
+        <v>67</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="28">
         <v>30.0</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="29">
         <f t="shared" si="1"/>
-        <v>0.7649305556</v>
+        <v>0.7454861111</v>
       </c>
-      <c r="F19" s="23"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -1590,24 +1777,28 @@
       <c r="AC19" s="5"/>
     </row>
     <row r="20">
-      <c r="A20" s="24">
+      <c r="A20" s="20">
         <v>18.0</v>
       </c>
-      <c r="B20" s="25" t="s">
-        <v>51</v>
+      <c r="B20" s="31" t="s">
+        <v>68</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>52</v>
+      <c r="C20" s="12" t="s">
+        <v>69</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="15">
         <v>5.0</v>
       </c>
       <c r="E20" s="17">
         <f t="shared" si="1"/>
-        <v>0.7857638889</v>
+        <v>0.7677083333</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="F20" s="15">
+        <v>2.0</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
@@ -1632,27 +1823,29 @@
       <c r="AC20" s="5"/>
     </row>
     <row r="21">
-      <c r="A21" s="24">
+      <c r="A21" s="20">
         <v>19.0</v>
       </c>
-      <c r="B21" s="26" t="s">
-        <v>53</v>
+      <c r="B21" s="21" t="s">
+        <v>71</v>
       </c>
-      <c r="C21" s="12" t="s">
-        <v>54</v>
+      <c r="C21" s="8" t="s">
+        <v>72</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="16">
         <v>5.0</v>
       </c>
       <c r="E21" s="17">
         <f t="shared" si="1"/>
-        <v>0.790625</v>
+        <v>0.7711805556</v>
       </c>
-      <c r="F21" s="15">
-        <v>2.0</v>
+      <c r="F21" s="4"/>
+      <c r="G21" s="2" t="s">
+        <v>73</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="H21" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
       <c r="K21" s="5"/>
@@ -1676,26 +1869,28 @@
       <c r="AC21" s="5"/>
     </row>
     <row r="22">
-      <c r="A22" s="18">
+      <c r="A22" s="2">
         <v>20.0</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D22" s="16">
         <v>5.0</v>
       </c>
       <c r="E22" s="17">
         <f t="shared" si="1"/>
-        <v>0.7954861111</v>
+        <v>0.7760416667</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="24">
         <v>2.0</v>
       </c>
-      <c r="G22" s="4"/>
+      <c r="G22" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
@@ -1720,32 +1915,32 @@
       <c r="AC22" s="5"/>
     </row>
     <row r="23">
-      <c r="A23" s="24">
+      <c r="A23" s="20">
         <v>21.0</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
-      <c r="C23" s="12" t="s">
-        <v>58</v>
+      <c r="C23" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="D23" s="16">
         <v>5.0</v>
       </c>
       <c r="E23" s="17">
         <f t="shared" si="1"/>
-        <v>0.8010416667</v>
+        <v>0.7815972222</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="24">
         <v>3.0</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
-        <v>59</v>
+      <c r="G23" s="18" t="s">
+        <v>80</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>60</v>
+      <c r="H23" s="19" t="s">
+        <v>81</v>
       </c>
+      <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -1768,26 +1963,28 @@
       <c r="AC23" s="5"/>
     </row>
     <row r="24">
-      <c r="A24" s="24">
+      <c r="A24" s="20">
         <v>22.0</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
-      <c r="C24" s="12" t="s">
-        <v>62</v>
+      <c r="C24" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="D24" s="16">
         <v>5.0</v>
       </c>
       <c r="E24" s="17">
         <f t="shared" si="1"/>
-        <v>0.8059027778</v>
+        <v>0.7864583333</v>
       </c>
       <c r="F24" s="15">
         <v>2.0</v>
       </c>
-      <c r="G24" s="4"/>
+      <c r="G24" s="32" t="s">
+        <v>84</v>
+      </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
@@ -1812,26 +2009,28 @@
       <c r="AC24" s="5"/>
     </row>
     <row r="25">
-      <c r="A25" s="18">
+      <c r="A25" s="20">
         <v>23.0</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="D25" s="16">
         <v>5.0</v>
       </c>
       <c r="E25" s="17">
         <f t="shared" si="1"/>
-        <v>0.8114583333</v>
+        <v>0.7913194444</v>
       </c>
       <c r="F25" s="15">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
-      <c r="G25" s="4"/>
+      <c r="G25" s="18" t="s">
+        <v>87</v>
+      </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="4"/>
@@ -1856,26 +2055,28 @@
       <c r="AC25" s="5"/>
     </row>
     <row r="26">
-      <c r="A26" s="24">
+      <c r="A26" s="20">
         <v>24.0</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>65</v>
+      <c r="B26" s="31" t="s">
+        <v>88</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>66</v>
+      <c r="C26" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="D26" s="16">
         <v>5.0</v>
       </c>
       <c r="E26" s="17">
         <f t="shared" si="1"/>
-        <v>0.8163194444</v>
+        <v>0.7961805556</v>
       </c>
       <c r="F26" s="15">
         <v>2.0</v>
       </c>
-      <c r="G26" s="4"/>
+      <c r="G26" s="2" t="s">
+        <v>89</v>
+      </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
@@ -1900,26 +2101,28 @@
       <c r="AC26" s="5"/>
     </row>
     <row r="27">
-      <c r="A27" s="24">
+      <c r="A27" s="20">
         <v>25.0</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D27" s="15">
         <v>5.0</v>
       </c>
       <c r="E27" s="17">
         <f t="shared" si="1"/>
-        <v>0.8211805556</v>
+        <v>0.8010416667</v>
       </c>
       <c r="F27" s="15">
         <v>2.0</v>
       </c>
-      <c r="G27" s="4"/>
+      <c r="G27" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="4"/>
@@ -1944,27 +2147,31 @@
       <c r="AC27" s="5"/>
     </row>
     <row r="28">
-      <c r="A28" s="18">
+      <c r="A28" s="2">
         <v>26.0</v>
       </c>
-      <c r="B28" s="26" t="s">
-        <v>69</v>
+      <c r="B28" s="31" t="s">
+        <v>93</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="D28" s="16">
         <v>5.0</v>
       </c>
       <c r="E28" s="17">
         <f t="shared" si="1"/>
-        <v>0.8274305556</v>
+        <v>0.8072916667</v>
       </c>
       <c r="F28" s="15">
         <v>4.0</v>
       </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="G28" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4"/>
       <c r="K28" s="5"/>
@@ -1988,27 +2195,31 @@
       <c r="AC28" s="5"/>
     </row>
     <row r="29">
-      <c r="A29" s="24">
+      <c r="A29" s="20">
         <v>27.0</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D29" s="16">
         <v>5.0</v>
       </c>
       <c r="E29" s="17">
         <f t="shared" si="1"/>
-        <v>0.8329861111</v>
+        <v>0.8128472222</v>
       </c>
       <c r="F29" s="15">
         <v>3.0</v>
       </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="G29" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>100</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4"/>
       <c r="K29" s="5"/>
@@ -2032,26 +2243,28 @@
       <c r="AC29" s="5"/>
     </row>
     <row r="30">
-      <c r="A30" s="24">
+      <c r="A30" s="20">
         <v>28.0</v>
       </c>
-      <c r="B30" s="26" t="s">
-        <v>73</v>
+      <c r="B30" s="31" t="s">
+        <v>101</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D30" s="16">
         <v>5.0</v>
       </c>
       <c r="E30" s="17">
         <f t="shared" si="1"/>
-        <v>0.8378472222</v>
+        <v>0.8177083333</v>
       </c>
       <c r="F30" s="15">
         <v>2.0</v>
       </c>
-      <c r="G30" s="4"/>
+      <c r="G30" s="2" t="s">
+        <v>103</v>
+      </c>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
@@ -2076,26 +2289,28 @@
       <c r="AC30" s="5"/>
     </row>
     <row r="31">
-      <c r="A31" s="18">
+      <c r="A31" s="2">
         <v>29.0</v>
       </c>
-      <c r="B31" s="26" t="s">
-        <v>75</v>
+      <c r="B31" s="31" t="s">
+        <v>104</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="D31" s="16">
         <v>5.0</v>
       </c>
       <c r="E31" s="17">
         <f t="shared" si="1"/>
-        <v>0.8427083333</v>
+        <v>0.8225694444</v>
       </c>
       <c r="F31" s="15">
         <v>2.0</v>
       </c>
-      <c r="G31" s="4"/>
+      <c r="G31" s="2" t="s">
+        <v>106</v>
+      </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4"/>
       <c r="J31" s="4"/>
@@ -2120,26 +2335,28 @@
       <c r="AC31" s="5"/>
     </row>
     <row r="32">
-      <c r="A32" s="24">
+      <c r="A32" s="20">
         <v>30.0</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>77</v>
+      <c r="B32" s="31" t="s">
+        <v>107</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="D32" s="16">
         <v>5.0</v>
       </c>
       <c r="E32" s="17">
         <f t="shared" si="1"/>
-        <v>0.8475694444</v>
+        <v>0.8274305556</v>
       </c>
       <c r="F32" s="15">
         <v>2.0</v>
       </c>
-      <c r="G32" s="4"/>
+      <c r="G32" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -2164,28 +2381,30 @@
       <c r="AC32" s="5"/>
     </row>
     <row r="33">
-      <c r="A33" s="24">
+      <c r="A33" s="2">
         <v>31.0</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="D33" s="16">
         <v>5.0</v>
       </c>
       <c r="E33" s="17">
         <f t="shared" si="1"/>
-        <v>0.8524305556</v>
+        <v>0.8329861111</v>
       </c>
       <c r="F33" s="15">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4" t="s">
-        <v>59</v>
+      <c r="G33" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>113</v>
       </c>
       <c r="I33" s="4"/>
       <c r="J33" s="4"/>
@@ -2210,26 +2429,28 @@
       <c r="AC33" s="5"/>
     </row>
     <row r="34">
-      <c r="A34" s="18">
+      <c r="A34" s="2">
         <v>32.0</v>
       </c>
-      <c r="B34" s="26" t="s">
-        <v>81</v>
+      <c r="B34" s="31" t="s">
+        <v>114</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="D34" s="15">
         <v>4.0</v>
       </c>
       <c r="E34" s="17">
         <f t="shared" si="1"/>
-        <v>0.8572916667</v>
+        <v>0.8378472222</v>
       </c>
       <c r="F34" s="15">
         <v>2.0</v>
       </c>
-      <c r="G34" s="4"/>
+      <c r="G34" s="2" t="s">
+        <v>116</v>
+      </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -2254,26 +2475,28 @@
       <c r="AC34" s="5"/>
     </row>
     <row r="35">
-      <c r="A35" s="24">
+      <c r="A35" s="20">
         <v>33.0</v>
       </c>
-      <c r="B35" s="26" t="s">
-        <v>69</v>
+      <c r="B35" s="31" t="s">
+        <v>93</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="D35" s="16">
         <v>5.0</v>
       </c>
       <c r="E35" s="17">
         <f t="shared" si="1"/>
-        <v>0.8621527778</v>
+        <v>0.8427083333</v>
       </c>
       <c r="F35" s="15">
         <v>3.0</v>
       </c>
-      <c r="G35" s="4"/>
+      <c r="G35" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
       <c r="J35" s="4"/>
@@ -2298,26 +2521,28 @@
       <c r="AC35" s="5"/>
     </row>
     <row r="36">
-      <c r="A36" s="24">
+      <c r="A36" s="20">
         <v>34.0</v>
       </c>
-      <c r="B36" s="26" t="s">
-        <v>84</v>
+      <c r="B36" s="31" t="s">
+        <v>119</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>85</v>
+      <c r="C36" s="8" t="s">
+        <v>120</v>
       </c>
       <c r="D36" s="16">
         <v>5.0</v>
       </c>
       <c r="E36" s="17">
         <f t="shared" si="1"/>
-        <v>0.8670138889</v>
+        <v>0.8475694444</v>
       </c>
       <c r="F36" s="15">
         <v>2.0</v>
       </c>
-      <c r="G36" s="4"/>
+      <c r="G36" s="32" t="s">
+        <v>121</v>
+      </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
@@ -2342,27 +2567,31 @@
       <c r="AC36" s="5"/>
     </row>
     <row r="37">
-      <c r="A37" s="18">
+      <c r="A37" s="20">
         <v>35.0</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>86</v>
+      <c r="B37" s="31" t="s">
+        <v>122</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="D37" s="16">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="E37" s="17">
         <f t="shared" si="1"/>
-        <v>0.8732638889</v>
+        <v>0.8538194444</v>
       </c>
       <c r="F37" s="15">
         <v>4.0</v>
       </c>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="G37" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>125</v>
+      </c>
       <c r="I37" s="4"/>
       <c r="J37" s="4"/>
       <c r="K37" s="5"/>
@@ -2386,26 +2615,28 @@
       <c r="AC37" s="5"/>
     </row>
     <row r="38">
-      <c r="A38" s="18">
+      <c r="A38" s="2">
         <v>36.0</v>
       </c>
-      <c r="B38" s="26" t="s">
-        <v>88</v>
+      <c r="B38" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="D38" s="16">
         <v>5.0</v>
       </c>
       <c r="E38" s="17">
         <f t="shared" si="1"/>
-        <v>0.878125</v>
+        <v>0.8621527778</v>
       </c>
       <c r="F38" s="15">
         <v>2.0</v>
       </c>
-      <c r="G38" s="4"/>
+      <c r="G38" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
@@ -2430,32 +2661,32 @@
       <c r="AC38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="24">
+      <c r="A39" s="20">
         <v>37.0</v>
       </c>
-      <c r="B39" s="26" t="s">
-        <v>90</v>
+      <c r="B39" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="D39" s="16">
         <v>10.0</v>
       </c>
       <c r="E39" s="17">
         <f t="shared" si="1"/>
-        <v>0.884375</v>
+        <v>0.8684027778</v>
       </c>
       <c r="F39" s="15">
         <v>4.0</v>
       </c>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4" t="s">
-        <v>92</v>
+      <c r="G39" s="32" t="s">
+        <v>131</v>
       </c>
-      <c r="I39" s="4" t="s">
-        <v>60</v>
+      <c r="H39" s="2" t="s">
+        <v>132</v>
       </c>
+      <c r="I39" s="4"/>
       <c r="J39" s="4"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
@@ -2478,28 +2709,28 @@
       <c r="AC39" s="5"/>
     </row>
     <row r="40">
-      <c r="A40" s="24">
+      <c r="A40" s="2">
         <v>38.0</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>94</v>
+      <c r="C40" s="8" t="s">
+        <v>134</v>
       </c>
       <c r="D40" s="16">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="E40" s="17">
         <f t="shared" si="1"/>
-        <v>0.8940972222</v>
+        <v>0.878125</v>
       </c>
       <c r="F40" s="15">
         <v>4.0</v>
       </c>
       <c r="G40" s="4"/>
-      <c r="H40" s="4" t="s">
-        <v>59</v>
+      <c r="H40" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
@@ -2524,20 +2755,20 @@
       <c r="AC40" s="5"/>
     </row>
     <row r="41">
-      <c r="A41" s="18">
+      <c r="A41" s="25">
         <v>39.0</v>
       </c>
-      <c r="B41" s="19" t="s">
-        <v>95</v>
+      <c r="B41" s="26" t="s">
+        <v>135</v>
       </c>
-      <c r="C41" s="18" t="s">
-        <v>96</v>
+      <c r="C41" s="25" t="s">
+        <v>136</v>
       </c>
-      <c r="D41" s="28">
+      <c r="D41" s="33">
         <v>60.0</v>
       </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="30"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="35"/>
       <c r="G41" s="4"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -2563,17 +2794,17 @@
       <c r="AC41" s="5"/>
     </row>
     <row r="42">
-      <c r="A42" s="24">
+      <c r="A42" s="20">
         <v>40.0</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="14">
+      <c r="E42" s="36">
         <v>0.9375</v>
       </c>
       <c r="F42" s="4"/>
@@ -2602,17 +2833,17 @@
       <c r="AC42" s="5"/>
     </row>
     <row r="43">
-      <c r="A43" s="24">
+      <c r="A43" s="20">
         <v>41.0</v>
       </c>
-      <c r="B43" s="26" t="s">
-        <v>99</v>
+      <c r="B43" s="31" t="s">
+        <v>139</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="D43" s="4"/>
-      <c r="E43" s="14">
+      <c r="E43" s="36">
         <v>0.96875</v>
       </c>
       <c r="F43" s="4"/>
@@ -2644,7 +2875,7 @@
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="12" t="s">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
